--- a/content_analysis_report.xlsx
+++ b/content_analysis_report.xlsx
@@ -10,15 +10,20 @@
     <sheet name="Статистика" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Платформы" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Пол" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Соц статус" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Формат" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Среднее по полу" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Среднее по платформе" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Среднее по формату" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Медиана по полу" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Медиана по платформе" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Медиана по формату" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Топ слов" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Формат" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Медиана_платформа" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Медиана_пол" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Медиана_формат" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Медиана_возраст" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Медиана_стаж" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Рейтинг_платформа" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Отзывы_платформа" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Пол_Платформа_Цена" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Формат_Платформа_Цена" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Пол_Формат_Цена" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Платформа_Формат_частоты" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Топ_слов" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Категории_контента" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -424,41 +429,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Возраст</t>
+        </is>
+      </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Возраст</t>
+          <t>Стаж</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Стаж</t>
+          <t>Оценка</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Оценка</t>
+          <t>Количество отзывов</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Количество отзывов</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
           <t>Стоимость часа</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
+      <c r="A2" t="n">
+        <v>90</v>
       </c>
       <c r="B2" t="n">
         <v>90</v>
@@ -472,161 +475,123 @@
       <c r="E2" t="n">
         <v>90</v>
       </c>
-      <c r="F2" t="n">
-        <v>90</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
+      <c r="A3" t="n">
+        <v>42.44</v>
       </c>
       <c r="B3" t="n">
-        <v>42.44</v>
+        <v>10.67</v>
       </c>
       <c r="C3" t="n">
-        <v>10.67</v>
+        <v>4.91</v>
       </c>
       <c r="D3" t="n">
+        <v>36.13</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2477.96</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="B4" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D4" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1633.82</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="D6" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C7" t="n">
         <v>4.91</v>
       </c>
-      <c r="E3" t="n">
-        <v>36.13</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2477.96</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>std</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>13.77</v>
-      </c>
-      <c r="C4" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E4" t="n">
-        <v>18.86</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1633.82</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>21</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>30</v>
-      </c>
-      <c r="C6" t="n">
+      <c r="D7" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="B8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="D8" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>64</v>
+      </c>
+      <c r="B9" t="n">
+        <v>37</v>
+      </c>
+      <c r="C9" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="E6" t="n">
-        <v>20.25</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="C7" t="n">
-        <v>11</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="E7" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>53.75</v>
-      </c>
-      <c r="C8" t="n">
-        <v>15</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="E8" t="n">
-        <v>54.75</v>
-      </c>
-      <c r="F8" t="n">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>max</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>64</v>
-      </c>
-      <c r="C9" t="n">
-        <v>37</v>
-      </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
-      </c>
-      <c r="F9" t="n">
         <v>9500</v>
       </c>
     </row>
@@ -652,38 +617,38 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Медианное значение: Стоимость часа</t>
+          <t>Среднее значение: Оценка</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>repetit.ru</t>
+          <t>profi.ru</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2900</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>profi.ru</t>
+          <t>avito.ru</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2750</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>avito.ru</t>
+          <t>repetit.ru</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1000</v>
+        <v>4.91</v>
       </c>
     </row>
   </sheetData>
@@ -703,43 +668,43 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Офлайн / онлайн</t>
+          <t>Платформа</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Медианное значение: Стоимость часа</t>
+          <t>Среднее значение: Количество отзывов</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>онлайн</t>
+          <t>profi.ru</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2650</v>
+        <v>37.23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>офлайн</t>
+          <t>repetit.ru</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2000</v>
+        <v>35.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>офлайн и онлайн</t>
+          <t>avito.ru</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1900</v>
+        <v>35.5</v>
       </c>
     </row>
   </sheetData>
@@ -748,6 +713,310 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Пол</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>avito.ru</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>profi.ru</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>repetit.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>М</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Офлайн / онлайн</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>avito.ru</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>profi.ru</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>repetit.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>онлайн</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>офлайн</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>офлайн и онлайн</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1900</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1900</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Пол</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>онлайн</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>офлайн</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>офлайн и онлайн</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2750</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>М</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2650</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2450</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Платформа</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>онлайн</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>офлайн</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>офлайн и онлайн</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>avito.ru</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>profi.ru</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>repetit.ru</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>13</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -966,6 +1235,112 @@
       </c>
       <c r="B21" t="n">
         <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Категория</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Количество упоминаний</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Индивидуальный подход</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Квалификация и образование</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Достижения</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Опыт</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Профессиональное развитие</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Онлайн-формат</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Маркетинговые ходы</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Экзамены</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1081,13 +1456,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Социальный статус</t>
+          <t>Офлайн / онлайн</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -1099,181 +1474,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Школьный преподаватель</t>
+          <t>офлайн</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Частный преподаватель</t>
+          <t>онлайн</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Учитель</t>
+          <t>офлайн и онлайн</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Кандидат наук</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Студент</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Магистрант</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Частный исполнитель</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Преподаватель университета</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Магистрантка физфака СПБГУ</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Выпускник МГТУ им. Н.Э. Баумана</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>учитель физики в профильном классе в МОУ «Гимназия № 11» г. Волгоград.</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Учитель физики</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Санкт-Петербургский государственный университет, математико-механический факультет, специальность «Фундаментальные математика и механика»</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>МФТИ, факультет инноваций и высоких технологий, направление – прикладная математика и информатика</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Институт дополнительного образования по дополнительной профессиональной программе, профессиональная переподготовка по программе профессионального образования «математика и методика преподавания»</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Научный сотрудник, Научно-исследовательский институт атомных реакторов, г. Димитровград</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Студент СГТУ</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>студент МФТИ</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1293,43 +1518,43 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Офлайн / онлайн</t>
+          <t>Платформа</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Количество</t>
+          <t>Медианное значение: Стоимость часа</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>офлайн</t>
+          <t>repetit.ru</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>онлайн</t>
+          <t>profi.ru</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>офлайн и онлайн</t>
+          <t>avito.ru</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -1354,28 +1579,28 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Среднее значение: Стоимость часа</t>
+          <t>Медианное значение: Стоимость часа</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>М</t>
+          <t>Ж</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2526.96</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ж</t>
+          <t>М</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2428.96</v>
+        <v>2500</v>
       </c>
     </row>
   </sheetData>
@@ -1395,43 +1620,43 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Платформа</t>
+          <t>Офлайн / онлайн</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Среднее значение: Стоимость часа</t>
+          <t>Медианное значение: Стоимость часа</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>profi.ru</t>
+          <t>онлайн</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2830.7</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>repetit.ru</t>
+          <t>офлайн</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2786.67</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>avito.ru</t>
+          <t>офлайн и онлайн</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1816.5</v>
+        <v>1900</v>
       </c>
     </row>
   </sheetData>
@@ -1445,49 +1670,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Офлайн / онлайн</t>
+          <t>Возрастная группа</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Среднее значение: Стоимость часа</t>
+          <t>Медианное значение: Стоимость часа</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>онлайн</t>
+          <t>56+</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2828.29</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>офлайн и онлайн</t>
+          <t>до 25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2321.05</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>офлайн</t>
+          <t>36–45</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2236.59</v>
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>46–55</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>26–35</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1250</v>
       </c>
     </row>
   </sheetData>
@@ -1501,13 +1746,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Пол</t>
+          <t>Группа стажа</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -1519,21 +1764,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ж</t>
+          <t>4–7</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>М</t>
+          <t>8–15</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2500</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1–3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>16+</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1450</v>
       </c>
     </row>
   </sheetData>
